--- a/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>GDEV</t>
   </si>
@@ -656,224 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44651</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44469</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>121300</v>
+      </c>
+      <c r="E8" s="3">
         <v>234100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>103100</v>
       </c>
-      <c r="F8" s="3">
-        <v>124800</v>
-      </c>
       <c r="G8" s="3">
-        <v>125800</v>
+        <v>128000</v>
       </c>
       <c r="H8" s="3">
+        <v>252800</v>
+      </c>
+      <c r="I8" s="3">
         <v>126100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>122600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>115200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>109600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>86700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>74400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>64500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>63300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>83200</v>
+        <v>39900</v>
       </c>
       <c r="E9" s="3">
+        <v>104400</v>
+      </c>
+      <c r="F9" s="3">
         <v>56500</v>
       </c>
-      <c r="F9" s="3">
-        <v>41800</v>
-      </c>
       <c r="G9" s="3">
-        <v>38700</v>
+        <v>46100</v>
       </c>
       <c r="H9" s="3">
+        <v>89400</v>
+      </c>
+      <c r="I9" s="3">
         <v>36700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>38500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>32500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>22600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>22000</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>150900</v>
+        <v>81400</v>
       </c>
       <c r="E10" s="3">
+        <v>129700</v>
+      </c>
+      <c r="F10" s="3">
         <v>46600</v>
       </c>
-      <c r="F10" s="3">
-        <v>83000</v>
-      </c>
       <c r="G10" s="3">
-        <v>87100</v>
+        <v>81900</v>
       </c>
       <c r="H10" s="3">
+        <v>163400</v>
+      </c>
+      <c r="I10" s="3">
         <v>89400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>84100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>82700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>78500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>60000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>47500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>41900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>41300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,8 +904,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -938,8 +952,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,35 +1002,38 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>63400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>125400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,34 +1049,37 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E15" s="3">
         <v>2900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3400</v>
       </c>
-      <c r="F15" s="3">
-        <v>1200</v>
-      </c>
       <c r="G15" s="3">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="H15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I15" s="3">
         <v>900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1065,7 +1088,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>200</v>
@@ -1073,14 +1096,17 @@
       <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E17" s="3">
         <v>232800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>200900</v>
       </c>
-      <c r="F17" s="3">
-        <v>77200</v>
-      </c>
       <c r="G17" s="3">
-        <v>82500</v>
+        <v>83900</v>
       </c>
       <c r="H17" s="3">
+        <v>202600</v>
+      </c>
+      <c r="I17" s="3">
         <v>100200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>99600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>226600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>125200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>93800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>69200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>76200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>53500</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-97800</v>
       </c>
-      <c r="F18" s="3">
-        <v>47600</v>
-      </c>
       <c r="G18" s="3">
-        <v>43300</v>
+        <v>44100</v>
       </c>
       <c r="H18" s="3">
+        <v>50200</v>
+      </c>
+      <c r="I18" s="3">
         <v>25900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>23000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-111400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,102 +1241,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E20" s="3">
         <v>11100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2900</v>
       </c>
-      <c r="F20" s="3">
-        <v>-10800</v>
-      </c>
       <c r="G20" s="3">
-        <v>-1100</v>
+        <v>-10100</v>
       </c>
       <c r="H20" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I20" s="3">
         <v>7100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>12800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>27000</v>
       </c>
       <c r="E21" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-99200</v>
       </c>
-      <c r="F21" s="3">
-        <v>38600</v>
-      </c>
       <c r="G21" s="3">
-        <v>45700</v>
+        <v>35700</v>
       </c>
       <c r="H21" s="3">
-        <v>32000</v>
+        <v>58500</v>
       </c>
       <c r="I21" s="3">
+        <v>34500</v>
+      </c>
+      <c r="J21" s="3">
         <v>19200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-97900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-14200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1311,22 +1351,22 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1349,75 +1389,81 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E23" s="3">
         <v>12400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-100800</v>
       </c>
-      <c r="F23" s="3">
-        <v>36800</v>
-      </c>
       <c r="G23" s="3">
-        <v>42100</v>
+        <v>34000</v>
       </c>
       <c r="H23" s="3">
+        <v>54800</v>
+      </c>
+      <c r="I23" s="3">
         <v>33000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-98600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="E24" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>800</v>
-      </c>
-      <c r="I24" s="3">
-        <v>300</v>
       </c>
       <c r="J24" s="3">
         <v>300</v>
@@ -1426,25 +1472,28 @@
         <v>300</v>
       </c>
       <c r="L24" s="3">
+        <v>300</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>11300</v>
+        <v>23700</v>
       </c>
       <c r="E26" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-100400</v>
       </c>
-      <c r="F26" s="3">
-        <v>34700</v>
-      </c>
       <c r="G26" s="3">
-        <v>40900</v>
+        <v>31600</v>
       </c>
       <c r="H26" s="3">
+        <v>52700</v>
+      </c>
+      <c r="I26" s="3">
         <v>32200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-98800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-15100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-11200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10400</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>11300</v>
+        <v>23700</v>
       </c>
       <c r="E27" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100400</v>
       </c>
-      <c r="F27" s="3">
-        <v>34200</v>
-      </c>
       <c r="G27" s="3">
-        <v>41200</v>
+        <v>31200</v>
       </c>
       <c r="H27" s="3">
+        <v>53100</v>
+      </c>
+      <c r="I27" s="3">
         <v>32300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-98800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10400</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,41 +1689,44 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3">
         <v>23400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-3000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-11500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-8800</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3">
-        <v>-4900</v>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>-4900</v>
       </c>
       <c r="L29" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="M29" s="3">
         <v>-2600</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,102 +1839,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2900</v>
       </c>
-      <c r="F32" s="3">
-        <v>10800</v>
-      </c>
       <c r="G32" s="3">
-        <v>1100</v>
+        <v>10100</v>
       </c>
       <c r="H32" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-7100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-12800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>11300</v>
+        <v>23700</v>
       </c>
       <c r="E33" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-77000</v>
       </c>
-      <c r="F33" s="3">
-        <v>31200</v>
-      </c>
       <c r="G33" s="3">
-        <v>29600</v>
+        <v>28200</v>
       </c>
       <c r="H33" s="3">
+        <v>41500</v>
+      </c>
+      <c r="I33" s="3">
         <v>23400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-103700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10400</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>11300</v>
+        <v>23700</v>
       </c>
       <c r="E35" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-77000</v>
       </c>
-      <c r="F35" s="3">
-        <v>31200</v>
-      </c>
       <c r="G35" s="3">
-        <v>29600</v>
+        <v>28200</v>
       </c>
       <c r="H35" s="3">
+        <v>41500</v>
+      </c>
+      <c r="I35" s="3">
         <v>23400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-103700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10400</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44651</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44469</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,38 +2136,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>68600</v>
+      </c>
+      <c r="F41" s="3">
         <v>86800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>131500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>91400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>83700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>142800</v>
       </c>
-      <c r="I41" s="3">
-        <v>105500</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3">
         <v>40900</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2097,20 +2184,23 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>69300</v>
+      </c>
+      <c r="F42" s="3">
         <v>50400</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2126,8 +2216,8 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -2144,38 +2234,41 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>39600</v>
+      </c>
+      <c r="F43" s="3">
         <v>42900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>34000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>44700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>46500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>42800</v>
       </c>
-      <c r="I43" s="3">
-        <v>44900</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>63500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2188,11 +2281,14 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2238,38 +2334,41 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F45" s="3">
         <v>8800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>9800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>22400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>9100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5600</v>
       </c>
-      <c r="I45" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>4800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,38 +2384,41 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>198600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>185300</v>
+      </c>
+      <c r="F46" s="3">
         <v>188900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>175300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>158500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>139300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>191100</v>
       </c>
-      <c r="I46" s="3">
-        <v>156300</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3">
         <v>109100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2332,29 +2434,32 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>18500</v>
+      </c>
+      <c r="F47" s="3">
         <v>21200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>43300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>36500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>36800</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2364,8 +2469,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2373,19 +2478,22 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>0</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2200</v>
+        <v>4200</v>
       </c>
       <c r="E48" s="3">
         <v>2400</v>
@@ -2394,23 +2502,23 @@
         <v>2200</v>
       </c>
       <c r="G48" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I48" s="3">
         <v>4100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3400</v>
       </c>
-      <c r="I48" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3">
         <v>2900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2423,41 +2531,44 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F49" s="3">
         <v>14800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>63500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>64500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>65900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3">
         <v>1600</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1600</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,11 +2581,14 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,38 +2684,41 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>83400</v>
+      </c>
+      <c r="F52" s="3">
         <v>94900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>98400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>111600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>125700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>116700</v>
       </c>
-      <c r="I52" s="3">
-        <v>113200</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>105200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2611,11 +2731,14 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,38 +2784,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>307500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>302200</v>
+      </c>
+      <c r="F54" s="3">
         <v>322000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>383000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>373300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>371700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>313000</v>
       </c>
-      <c r="I54" s="3">
-        <v>273700</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3">
         <v>218900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2708,8 +2834,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,38 +2876,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F57" s="3">
         <v>22300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>8300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>22100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>16200</v>
       </c>
-      <c r="I57" s="3">
-        <v>19400</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>20900</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,38 +2924,41 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
         <v>700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
-        <v>900</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3">
         <v>1300</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2837,41 +2971,44 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>286100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>312300</v>
+      </c>
+      <c r="F59" s="3">
         <v>309400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>302800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>316300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>319200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>305800</v>
       </c>
-      <c r="I59" s="3">
-        <v>293700</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>275900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2887,38 +3024,41 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>301300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>328100</v>
+      </c>
+      <c r="F60" s="3">
         <v>332400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>311800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>326800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>342900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>322800</v>
       </c>
-      <c r="I60" s="3">
-        <v>313900</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3">
         <v>298100</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2934,38 +3074,41 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E61" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>400</v>
       </c>
       <c r="G61" s="3">
+        <v>600</v>
+      </c>
+      <c r="H61" s="3">
+        <v>400</v>
+      </c>
+      <c r="I61" s="3">
         <v>900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1100</v>
       </c>
-      <c r="I61" s="3">
-        <v>500</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2981,38 +3124,41 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>116700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>109700</v>
+      </c>
+      <c r="F62" s="3">
         <v>138000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>144100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>151200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>166900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>150100</v>
       </c>
-      <c r="I62" s="3">
-        <v>137900</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>105600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3028,8 +3174,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,38 +3324,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>419000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>437900</v>
+      </c>
+      <c r="F66" s="3">
         <v>470800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>456600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>478200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>510700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>474100</v>
       </c>
-      <c r="I66" s="3">
-        <v>452300</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3">
         <v>404200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3216,8 +3374,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,38 +3594,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-136200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-159800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-172500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-73600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-104900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-139000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-161100</v>
       </c>
-      <c r="I72" s="3">
-        <v>-178600</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
         <v>-185400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3644,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,38 +3794,41 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-111500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-135800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-148800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-73600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-104900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-139000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-161100</v>
       </c>
-      <c r="I76" s="3">
-        <v>-178600</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
         <v>-185400</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,8 +3844,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44651</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44469</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>11300</v>
+        <v>23700</v>
       </c>
       <c r="E81" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-77000</v>
       </c>
-      <c r="F81" s="3">
-        <v>31200</v>
-      </c>
       <c r="G81" s="3">
-        <v>29600</v>
+        <v>28200</v>
       </c>
       <c r="H81" s="3">
+        <v>41500</v>
+      </c>
+      <c r="I81" s="3">
         <v>23400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-103700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10400</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,40 +4021,41 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>1700</v>
       </c>
       <c r="E83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F83" s="3">
         <v>1500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3600</v>
       </c>
-      <c r="H83" s="3">
-        <v>-1100</v>
-      </c>
       <c r="I83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J83" s="3">
         <v>800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>600</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
       </c>
       <c r="L83" s="3">
+        <v>600</v>
+      </c>
+      <c r="M83" s="3">
         <v>500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>200</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
@@ -3865,13 +4064,16 @@
         <v>200</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>8000</v>
       </c>
       <c r="E89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F89" s="3">
         <v>16800</v>
       </c>
-      <c r="F89" s="3">
-        <v>59800</v>
-      </c>
       <c r="G89" s="3">
-        <v>39500</v>
+        <v>59700</v>
       </c>
       <c r="H89" s="3">
-        <v>-87100</v>
+        <v>39600</v>
       </c>
       <c r="I89" s="3">
+        <v>18400</v>
+      </c>
+      <c r="J89" s="3">
         <v>43700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>51000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>41500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>40000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,55 +4391,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-400</v>
       </c>
       <c r="K91" s="3">
         <v>-400</v>
       </c>
       <c r="L91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4539,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-14200</v>
       </c>
       <c r="E94" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-63100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-25400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-83300</v>
       </c>
-      <c r="H94" s="3">
-        <v>-74300</v>
-      </c>
       <c r="I94" s="3">
+        <v>-77100</v>
+      </c>
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1400</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4425,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,145 +4809,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>-1200</v>
       </c>
       <c r="E100" s="3">
-        <v>-300</v>
+        <v>-800</v>
       </c>
       <c r="F100" s="3">
         <v>-300</v>
       </c>
       <c r="G100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1400</v>
       </c>
-      <c r="H100" s="3">
-        <v>42300</v>
-      </c>
       <c r="I100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J100" s="3">
         <v>-5500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>14100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-50700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-34000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-200</v>
       </c>
       <c r="E101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>1800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1400</v>
       </c>
-      <c r="H101" s="3">
-        <v>1800</v>
-      </c>
       <c r="I101" s="3">
+        <v>200</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1100</v>
-      </c>
-      <c r="N101" s="3">
-        <v>400</v>
       </c>
       <c r="O101" s="3">
         <v>400</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>-7600</v>
       </c>
       <c r="E102" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-44800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>32400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-43700</v>
       </c>
-      <c r="H102" s="3">
-        <v>-117300</v>
-      </c>
       <c r="I102" s="3">
+        <v>-59100</v>
+      </c>
+      <c r="J102" s="3">
         <v>37300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>64600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-59000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>35400</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
   <si>
     <t>GDEV</t>
   </si>
@@ -656,237 +656,249 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>109100</v>
+      </c>
+      <c r="E8" s="3">
         <v>121300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>234100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>103100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>128000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>252800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>126100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>122600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>115200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>109600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>86700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>74400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>64500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>63300</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E9" s="3">
         <v>39900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>104400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>56500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>46100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>89400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>38500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>32500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>31100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>22600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>22000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E10" s="3">
         <v>81400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>129700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>46600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>81900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>163400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>89400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>84100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>82700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>78500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>60000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>47500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>41900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>41300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +917,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +968,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,38 +1021,41 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>63400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>125400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1052,37 +1071,40 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E15" s="3">
         <v>1700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
@@ -1091,7 +1113,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>200</v>
@@ -1099,14 +1121,17 @@
       <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>200</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1147,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E17" s="3">
         <v>92300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>232800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>200900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>83900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>202600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>100200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>99600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>226600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>125200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>93800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>69200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>76200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>53500</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E18" s="3">
         <v>29000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-97800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>44100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>50200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>25900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>23000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-111400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9800</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,108 +1274,115 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>11100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E21" s="3">
         <v>27000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-99200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>35700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>58500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>34500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-97900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-14200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1354,22 +1393,22 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1392,81 +1431,87 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E23" s="3">
         <v>25300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-100800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>34000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>54800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>33000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-98600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10600</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>800</v>
-      </c>
-      <c r="J24" s="3">
-        <v>300</v>
       </c>
       <c r="K24" s="3">
         <v>300</v>
@@ -1475,25 +1520,28 @@
         <v>300</v>
       </c>
       <c r="M24" s="3">
+        <v>300</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
-      </c>
-      <c r="O24" s="3">
-        <v>200</v>
       </c>
       <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>200</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1590,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E26" s="3">
         <v>23700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-100400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>31600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>52700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>32200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-98800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10400</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E27" s="3">
         <v>23700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>23800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-100400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>31200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>53100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>32300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-98800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10400</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1703,33 +1763,33 @@
       <c r="E29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3">
         <v>23400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-3000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-11500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-8800</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="3">
-        <v>-4900</v>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>-4900</v>
       </c>
       <c r="M29" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="N29" s="3">
         <v>-2600</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
@@ -1742,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1908,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E32" s="3">
         <v>3700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-11100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E33" s="3">
         <v>23700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>23800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-77000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>28200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>41500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>23400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-103700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10400</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2067,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E35" s="3">
         <v>23700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>23800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-77000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>28200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>41500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>23400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-103700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10400</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,41 +2222,42 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E41" s="3">
         <v>61000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>86800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>131500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>91400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>83700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>142800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3">
         <v>40900</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2187,23 +2273,26 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>84200</v>
+      </c>
+      <c r="E42" s="3">
         <v>83900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>69300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>50400</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2219,8 +2308,8 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -2237,41 +2326,44 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E43" s="3">
         <v>44600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>39600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>42900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>34000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>44700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>42800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
         <v>63500</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,11 +2376,14 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2337,41 +2432,44 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E45" s="3">
         <v>9100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5600</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>4800</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2387,41 +2485,44 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>213900</v>
+      </c>
+      <c r="E46" s="3">
         <v>198600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>185300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>188900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>175300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>158500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>139300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>191100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3">
         <v>109100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2437,32 +2538,35 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E47" s="3">
         <v>16200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>18500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>21200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>43300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>36500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>36800</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2472,8 +2576,8 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2481,47 +2585,50 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>0</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E48" s="3">
         <v>4200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3400</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3">
         <v>2900</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2534,44 +2641,47 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E49" s="3">
         <v>11400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>63500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>64500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>65900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1800</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3">
         <v>1600</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2584,11 +2694,14 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,41 +2803,44 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E52" s="3">
         <v>77100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>83400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>94900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>98400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>111600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>125700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>116700</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
         <v>105200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2734,11 +2853,14 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,41 +2909,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>320600</v>
+      </c>
+      <c r="E54" s="3">
         <v>307500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>302200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>322000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>383000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>373300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>371700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>313000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3">
         <v>218900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2837,8 +2962,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,41 +3006,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E57" s="3">
         <v>14000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>20900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,41 +3057,44 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>700</v>
       </c>
       <c r="G58" s="3">
         <v>700</v>
       </c>
       <c r="H58" s="3">
+        <v>700</v>
+      </c>
+      <c r="I58" s="3">
         <v>900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
         <v>1300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2974,44 +3107,47 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>279600</v>
+      </c>
+      <c r="E59" s="3">
         <v>286100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>312300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>309400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>302800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>316300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>319200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>305800</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>275900</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,41 +3163,44 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>302800</v>
+      </c>
+      <c r="E60" s="3">
         <v>301300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>328100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>332400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>311800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>326800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>342900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>322800</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3">
         <v>298100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3077,8 +3216,11 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3086,32 +3228,32 @@
         <v>1000</v>
       </c>
       <c r="E61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3127,41 +3269,44 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>116600</v>
+      </c>
+      <c r="E62" s="3">
         <v>116700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>109700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>138000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>144100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>151200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>166900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>150100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>105600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3177,8 +3322,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,41 +3481,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>420400</v>
+      </c>
+      <c r="E66" s="3">
         <v>419000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>437900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>470800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>456600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>478200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>510700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>474100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3">
         <v>404200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3377,8 +3534,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,41 +3767,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-125300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-136200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-159800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-172500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-73600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-104900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-139000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-161100</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
         <v>-185400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3820,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,41 +3979,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-99800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-111500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-135800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-148800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-73600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-104900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-139000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-161100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3">
         <v>-185400</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3847,8 +4032,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4085,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E81" s="3">
         <v>23700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>23800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-77000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>28200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>41500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>23400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-103700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10400</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,43 +4219,44 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>600</v>
       </c>
       <c r="L83" s="3">
         <v>600</v>
       </c>
       <c r="M83" s="3">
+        <v>600</v>
+      </c>
+      <c r="N83" s="3">
         <v>500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
@@ -4067,13 +4265,16 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4535,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E89" s="3">
         <v>8000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>59700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>39600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>18400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>43700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>51000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>41500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>32400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>40000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,58 +4611,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-400</v>
       </c>
       <c r="L91" s="3">
         <v>-400</v>
       </c>
       <c r="M91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4768,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-63100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-83300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-77100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1400</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4662,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,154 +5054,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-800</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-300</v>
       </c>
       <c r="G100" s="3">
         <v>-300</v>
       </c>
       <c r="H100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>14100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-50700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-34000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1100</v>
-      </c>
-      <c r="O101" s="3">
-        <v>400</v>
       </c>
       <c r="P101" s="3">
         <v>400</v>
       </c>
       <c r="Q101" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-44800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>32400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-43700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-59100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>37300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>64600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-59000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>35400</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>GDEV</t>
   </si>
@@ -656,249 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
-        <v>44834</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>105800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>106900</v>
+      </c>
+      <c r="F8" s="3">
         <v>109100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>121300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>234100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
+        <v>119300</v>
+      </c>
+      <c r="J8" s="3">
         <v>103100</v>
       </c>
-      <c r="H8" s="3">
-        <v>128000</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>252800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>126100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>122600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>115200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>109600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>86700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>74400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>64500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>63300</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>36200</v>
+      </c>
+      <c r="F9" s="3">
         <v>37600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>39900</v>
       </c>
-      <c r="F9" s="3">
-        <v>104400</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>208500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>43400</v>
+      </c>
+      <c r="J9" s="3">
         <v>56500</v>
       </c>
-      <c r="H9" s="3">
-        <v>46100</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>89400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>36700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>38500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>32500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>31100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>26700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>26900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>22600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>22000</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>70700</v>
+      </c>
+      <c r="F10" s="3">
         <v>71500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>81400</v>
       </c>
-      <c r="F10" s="3">
-        <v>129700</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>25600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>75900</v>
+      </c>
+      <c r="J10" s="3">
         <v>46600</v>
       </c>
-      <c r="H10" s="3">
-        <v>81900</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>163400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>89400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>84100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>82700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>78500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>60000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>47500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>41900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>41300</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,8 +945,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -971,8 +1000,14 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,44 +1059,50 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>63400</v>
       </c>
-      <c r="H14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>125400</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1074,64 +1115,76 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3">
         <v>1600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1700</v>
       </c>
-      <c r="F15" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3">
         <v>3400</v>
       </c>
-      <c r="H15" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>3600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>100</v>
-      </c>
-      <c r="M15" s="3">
-        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>200</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
+      <c r="R15" s="3">
+        <v>200</v>
       </c>
       <c r="S15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,114 +1201,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>108800</v>
+      </c>
+      <c r="F17" s="3">
         <v>101000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>92300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>232800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
+        <v>132700</v>
+      </c>
+      <c r="J17" s="3">
         <v>200900</v>
       </c>
-      <c r="H17" s="3">
-        <v>83900</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>202600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>100200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>99600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>226600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>125200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>93800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>69200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>76200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>53500</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F18" s="3">
         <v>8100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>29000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="J18" s="3">
         <v>-97800</v>
       </c>
-      <c r="H18" s="3">
-        <v>44100</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>50200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>25900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>23000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-111400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-15600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-7100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>5200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>9800</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,146 +1342,160 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F20" s="3">
         <v>4300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-3700</v>
       </c>
-      <c r="F20" s="3">
-        <v>11100</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>12100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2900</v>
       </c>
-      <c r="H20" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>7100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-4600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>12800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F21" s="3">
         <v>13900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>27000</v>
       </c>
-      <c r="F21" s="3">
-        <v>15300</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>16300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="J21" s="3">
         <v>-99200</v>
       </c>
-      <c r="H21" s="3">
-        <v>35700</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>58500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>34500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>19200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-97900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-14200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-8500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>6700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>10800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1434,96 +1515,108 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F23" s="3">
         <v>12300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>25300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>12400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="J23" s="3">
         <v>-100800</v>
       </c>
-      <c r="H23" s="3">
-        <v>34000</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>54800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>33000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>18300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-98600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-14800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-8900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>6600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>10600</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>900</v>
+      </c>
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
-        <v>13500</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I24" s="3">
+        <v>700</v>
+      </c>
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
-      </c>
-      <c r="K24" s="3">
-        <v>300</v>
-      </c>
-      <c r="L24" s="3">
-        <v>300</v>
       </c>
       <c r="M24" s="3">
         <v>300</v>
       </c>
       <c r="N24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O24" s="3">
         <v>300</v>
@@ -1532,16 +1625,22 @@
         <v>200</v>
       </c>
       <c r="Q24" s="3">
+        <v>300</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1692,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F26" s="3">
         <v>11100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>23700</v>
       </c>
-      <c r="F26" s="3">
-        <v>12400</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>11300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="J26" s="3">
         <v>-100400</v>
       </c>
-      <c r="H26" s="3">
-        <v>31600</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>52700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>32200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>18100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-98800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-15100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-9100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>6300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>10400</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F27" s="3">
         <v>11100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>23700</v>
       </c>
-      <c r="F27" s="3">
-        <v>23800</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>11300</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="J27" s="3">
         <v>-100400</v>
       </c>
-      <c r="H27" s="3">
-        <v>31200</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>53100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>32300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>18000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-98800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-15100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-9100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>6300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>10400</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1869,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1766,36 +1889,36 @@
       <c r="F29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3">
+        <v>208700</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3">
         <v>23400</v>
       </c>
-      <c r="H29" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-11500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-8800</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3">
         <v>-4900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-4900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-2600</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
@@ -1805,8 +1928,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1987,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,114 +2046,132 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>3700</v>
       </c>
-      <c r="F32" s="3">
-        <v>-11100</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="J32" s="3">
         <v>2900</v>
       </c>
-      <c r="H32" s="3">
-        <v>10100</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-7100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>4600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-12800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F33" s="3">
         <v>11100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>23700</v>
       </c>
-      <c r="F33" s="3">
-        <v>23800</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>220000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="J33" s="3">
         <v>-77000</v>
       </c>
-      <c r="H33" s="3">
-        <v>28200</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>41500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>23400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>18000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-103700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-20000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-11800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>6300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>10400</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2223,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F35" s="3">
         <v>11100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>23700</v>
       </c>
-      <c r="F35" s="3">
-        <v>23800</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>220000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="J35" s="3">
         <v>-77000</v>
       </c>
-      <c r="H35" s="3">
-        <v>28200</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>41500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>23400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>18000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-103700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-20000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-11800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>6300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>10400</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
-        <v>44834</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2373,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,47 +2396,49 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>68300</v>
+      </c>
+      <c r="F41" s="3">
         <v>71800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>61000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>68600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>84600</v>
+      </c>
+      <c r="J41" s="3">
         <v>86800</v>
       </c>
-      <c r="H41" s="3">
-        <v>131500</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>91400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>83700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>142800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3">
         <v>40900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,32 +2451,38 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E42" s="3">
+        <v>56500</v>
+      </c>
+      <c r="F42" s="3">
         <v>84200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>83900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>69300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
+        <v>27200</v>
+      </c>
+      <c r="J42" s="3">
         <v>50400</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2311,11 +2492,11 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2329,47 +2510,53 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>41800</v>
+      </c>
+      <c r="F43" s="3">
         <v>48800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>44600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>39600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
+        <v>51500</v>
+      </c>
+      <c r="J43" s="3">
         <v>42900</v>
       </c>
-      <c r="H43" s="3">
-        <v>34000</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>44700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>46500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>42800</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3">
         <v>63500</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2379,11 +2566,17 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2435,47 +2628,53 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F45" s="3">
         <v>9000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>9100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>7900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J45" s="3">
         <v>8800</v>
       </c>
-      <c r="H45" s="3">
-        <v>9800</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>22400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>9100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>5600</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3">
         <v>4800</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,47 +2687,53 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>162900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>172400</v>
+      </c>
+      <c r="F46" s="3">
         <v>213900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>198600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>185300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>165900</v>
+      </c>
+      <c r="J46" s="3">
         <v>188900</v>
       </c>
-      <c r="H46" s="3">
-        <v>175300</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>158500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>139300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>191100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3">
         <v>109100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2541,100 +2746,112 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F47" s="3">
         <v>18100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>16200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>18500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
+        <v>17300</v>
+      </c>
+      <c r="J47" s="3">
         <v>21200</v>
       </c>
-      <c r="H47" s="3">
-        <v>43300</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>36500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>36800</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F48" s="3">
         <v>4100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2200</v>
       </c>
       <c r="H48" s="3">
         <v>2400</v>
       </c>
       <c r="I48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J48" s="3">
         <v>2200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L48" s="3">
         <v>4100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3400</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3">
         <v>2900</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2644,50 +2861,56 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F49" s="3">
         <v>10300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>11400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>12600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
+        <v>9200</v>
+      </c>
+      <c r="J49" s="3">
         <v>14800</v>
       </c>
-      <c r="H49" s="3">
-        <v>63500</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>64500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>65900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1800</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3">
         <v>1600</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2697,11 +2920,17 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2982,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,47 +3041,53 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>87700</v>
+      </c>
+      <c r="F52" s="3">
         <v>74200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>77100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>83400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
+        <v>73300</v>
+      </c>
+      <c r="J52" s="3">
         <v>94900</v>
       </c>
-      <c r="H52" s="3">
-        <v>98400</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>111600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>125700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>116700</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3">
         <v>105200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,11 +3097,17 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,47 +3159,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>282800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>295600</v>
+      </c>
+      <c r="F54" s="3">
         <v>320600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>307500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>302200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>269300</v>
+      </c>
+      <c r="J54" s="3">
         <v>322000</v>
       </c>
-      <c r="H54" s="3">
-        <v>383000</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>373300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>371700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>313000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3">
         <v>218900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3218,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3245,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,47 +3268,49 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>32700</v>
+      </c>
+      <c r="F57" s="3">
         <v>21700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>14000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>15000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
+        <v>28500</v>
+      </c>
+      <c r="J57" s="3">
         <v>22300</v>
       </c>
-      <c r="H57" s="3">
-        <v>8300</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>9700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>22100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>16200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3">
         <v>20900</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3060,47 +3323,53 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>700</v>
+      </c>
+      <c r="F58" s="3">
         <v>1500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="H58" s="3">
-        <v>700</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>800</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>1300</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3110,50 +3379,56 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>265800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>290600</v>
+      </c>
+      <c r="F59" s="3">
         <v>279600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>286100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>312300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
+        <v>252600</v>
+      </c>
+      <c r="J59" s="3">
         <v>309400</v>
       </c>
-      <c r="H59" s="3">
-        <v>302800</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>316300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>319200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>305800</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3">
         <v>275900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3166,47 +3441,53 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>281100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>324000</v>
+      </c>
+      <c r="F60" s="3">
         <v>302800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>301300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>328100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>282200</v>
+      </c>
+      <c r="J60" s="3">
         <v>332400</v>
       </c>
-      <c r="H60" s="3">
-        <v>311800</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>326800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>342900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>322800</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3">
         <v>298100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,8 +3500,14 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3228,38 +3515,38 @@
         <v>1000</v>
       </c>
       <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
         <v>1000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
+        <v>900</v>
+      </c>
+      <c r="J61" s="3">
         <v>400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
+        <v>400</v>
+      </c>
+      <c r="L61" s="3">
+        <v>900</v>
+      </c>
+      <c r="M61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
-        <v>400</v>
-      </c>
-      <c r="J61" s="3">
-        <v>900</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>600</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3272,47 +3559,53 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>128200</v>
+      </c>
+      <c r="F62" s="3">
         <v>116600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>116700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>109700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
+        <v>120100</v>
+      </c>
+      <c r="J62" s="3">
         <v>138000</v>
       </c>
-      <c r="H62" s="3">
-        <v>144100</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>151200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>166900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>150100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
         <v>105600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,8 +3618,14 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3677,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3736,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,47 +3795,53 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>401500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>452400</v>
+      </c>
+      <c r="F66" s="3">
         <v>420400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>419000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>437900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
+        <v>403200</v>
+      </c>
+      <c r="J66" s="3">
         <v>470800</v>
       </c>
-      <c r="H66" s="3">
-        <v>456600</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>478200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>510700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>474100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3">
         <v>404200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3854,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3881,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3936,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3995,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +4054,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,47 +4113,53 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-111300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-156800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-125300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-136200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-159800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="J72" s="3">
         <v>-172500</v>
       </c>
-      <c r="H72" s="3">
-        <v>-73600</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-104900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-139000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-161100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3">
         <v>-185400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3823,8 +4172,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4231,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4290,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,47 +4349,53 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-156800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-99800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-111500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-135800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="J76" s="3">
         <v>-148800</v>
       </c>
-      <c r="H76" s="3">
-        <v>-73600</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-104900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-139000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-161100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3">
         <v>-185400</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4035,8 +4408,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4467,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
-        <v>44834</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F81" s="3">
         <v>11100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>23700</v>
       </c>
-      <c r="F81" s="3">
-        <v>23800</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>220000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="J81" s="3">
         <v>-77000</v>
       </c>
-      <c r="H81" s="3">
-        <v>28200</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>41500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>23400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>18000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-103700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-20000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-11800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>6300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>10400</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,61 +4617,69 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G83" s="3">
         <v>1700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>2900</v>
       </c>
-      <c r="G83" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1700</v>
-      </c>
       <c r="I83" s="3">
-        <v>3600</v>
+        <v>1400</v>
       </c>
       <c r="J83" s="3">
         <v>1500</v>
       </c>
       <c r="K83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M83" s="3">
         <v>800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4731,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4790,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4849,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4908,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4967,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>400</v>
+      </c>
+      <c r="F89" s="3">
         <v>10000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>8000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="J89" s="3">
         <v>16800</v>
       </c>
-      <c r="H89" s="3">
-        <v>59700</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>39600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>18400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>43700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>51000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-7700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>18500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>41500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>32400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>40000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,22 +5053,24 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-400</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-300</v>
@@ -4636,37 +5079,43 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +5167,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,61 +5226,73 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-45300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>56000</v>
+      </c>
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-14200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-18300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="J94" s="3">
         <v>-63100</v>
       </c>
-      <c r="H94" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-83300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-77100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1400</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5312,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4898,8 +5367,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5426,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5485,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,163 +5544,187 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-5500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>14100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-50700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-34000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-5100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J101" s="3">
         <v>1800</v>
       </c>
-      <c r="H101" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-33900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F102" s="3">
         <v>10800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-7600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-18200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="J102" s="3">
         <v>-44800</v>
       </c>
-      <c r="H102" s="3">
-        <v>32400</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-43700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-59100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>37300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>64600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-59000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>15400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>8600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>23400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>35400</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>GDEV</t>
   </si>
@@ -765,7 +765,7 @@
         <v>121300</v>
       </c>
       <c r="H8" s="3">
-        <v>234100</v>
+        <v>114900</v>
       </c>
       <c r="I8" s="3">
         <v>119300</v>
@@ -824,7 +824,7 @@
         <v>39900</v>
       </c>
       <c r="H9" s="3">
-        <v>208500</v>
+        <v>40700</v>
       </c>
       <c r="I9" s="3">
         <v>43400</v>
@@ -877,13 +877,13 @@
         <v>70700</v>
       </c>
       <c r="F10" s="3">
-        <v>71500</v>
+        <v>71600</v>
       </c>
       <c r="G10" s="3">
         <v>81400</v>
       </c>
       <c r="H10" s="3">
-        <v>25600</v>
+        <v>74200</v>
       </c>
       <c r="I10" s="3">
         <v>75900</v>
@@ -1070,20 +1070,20 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>400</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>2900</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1129,11 +1129,11 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1600</v>
       </c>
       <c r="F15" s="3">
         <v>1600</v>
@@ -1142,10 +1142,10 @@
         <v>1700</v>
       </c>
       <c r="H15" s="3">
-        <v>7200</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1400</v>
       </c>
       <c r="J15" s="3">
         <v>3400</v>
@@ -1215,19 +1215,19 @@
         <v>108800</v>
       </c>
       <c r="F17" s="3">
-        <v>101000</v>
+        <v>101100</v>
       </c>
       <c r="G17" s="3">
         <v>92300</v>
       </c>
       <c r="H17" s="3">
-        <v>232800</v>
+        <v>100100</v>
       </c>
       <c r="I17" s="3">
         <v>132700</v>
       </c>
       <c r="J17" s="3">
-        <v>200900</v>
+        <v>137500</v>
       </c>
       <c r="K17" s="3">
         <v>202600</v>
@@ -1274,19 +1274,19 @@
         <v>-1900</v>
       </c>
       <c r="F18" s="3">
-        <v>8100</v>
+        <v>8000</v>
       </c>
       <c r="G18" s="3">
         <v>29000</v>
       </c>
       <c r="H18" s="3">
-        <v>1300</v>
+        <v>14800</v>
       </c>
       <c r="I18" s="3">
-        <v>-13400</v>
+        <v>-13500</v>
       </c>
       <c r="J18" s="3">
-        <v>-97800</v>
+        <v>-34500</v>
       </c>
       <c r="K18" s="3">
         <v>50200</v>
@@ -1350,25 +1350,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>700</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
-        <v>1400</v>
+        <v>-3800</v>
       </c>
       <c r="F20" s="3">
-        <v>4300</v>
+        <v>-4100</v>
       </c>
       <c r="G20" s="3">
-        <v>-3700</v>
+        <v>4800</v>
       </c>
       <c r="H20" s="3">
-        <v>12100</v>
+        <v>-5300</v>
       </c>
       <c r="I20" s="3">
-        <v>6000</v>
+        <v>-4700</v>
       </c>
       <c r="J20" s="3">
-        <v>-2900</v>
+        <v>3600</v>
       </c>
       <c r="K20" s="3">
         <v>4700</v>
@@ -1409,25 +1409,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>17100</v>
+        <v>15800</v>
       </c>
       <c r="E21" s="3">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="F21" s="3">
-        <v>13900</v>
+        <v>13700</v>
       </c>
       <c r="G21" s="3">
-        <v>27000</v>
+        <v>25900</v>
       </c>
       <c r="H21" s="3">
-        <v>16300</v>
+        <v>21600</v>
       </c>
       <c r="I21" s="3">
-        <v>-6000</v>
+        <v>-7300</v>
       </c>
       <c r="J21" s="3">
-        <v>-99200</v>
+        <v>-34700</v>
       </c>
       <c r="K21" s="3">
         <v>58500</v>
@@ -1470,8 +1470,8 @@
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
+      <c r="E22" s="3">
+        <v>2500</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1539,7 +1539,7 @@
         <v>25300</v>
       </c>
       <c r="H23" s="3">
-        <v>12400</v>
+        <v>19800</v>
       </c>
       <c r="I23" s="3">
         <v>-7400</v>
@@ -1598,7 +1598,7 @@
         <v>1600</v>
       </c>
       <c r="H24" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="I24" s="3">
         <v>700</v>
@@ -1716,7 +1716,7 @@
         <v>23700</v>
       </c>
       <c r="H26" s="3">
-        <v>11300</v>
+        <v>19500</v>
       </c>
       <c r="I26" s="3">
         <v>-8200</v>
@@ -1775,13 +1775,13 @@
         <v>23700</v>
       </c>
       <c r="H27" s="3">
-        <v>11300</v>
+        <v>19500</v>
       </c>
       <c r="I27" s="3">
         <v>-8200</v>
       </c>
       <c r="J27" s="3">
-        <v>-100400</v>
+        <v>-77000</v>
       </c>
       <c r="K27" s="3">
         <v>53100</v>
@@ -1880,23 +1880,23 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>208700</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>23400</v>
@@ -2058,25 +2058,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-700</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
-        <v>-1400</v>
+        <v>3800</v>
       </c>
       <c r="F32" s="3">
-        <v>-4300</v>
+        <v>4100</v>
       </c>
       <c r="G32" s="3">
-        <v>3700</v>
+        <v>-4800</v>
       </c>
       <c r="H32" s="3">
-        <v>-12100</v>
+        <v>5300</v>
       </c>
       <c r="I32" s="3">
-        <v>-6000</v>
+        <v>4700</v>
       </c>
       <c r="J32" s="3">
-        <v>2900</v>
+        <v>-3600</v>
       </c>
       <c r="K32" s="3">
         <v>-4700</v>
@@ -2129,7 +2129,7 @@
         <v>23700</v>
       </c>
       <c r="H33" s="3">
-        <v>220000</v>
+        <v>19500</v>
       </c>
       <c r="I33" s="3">
         <v>-8200</v>
@@ -2247,7 +2247,7 @@
         <v>23700</v>
       </c>
       <c r="H35" s="3">
-        <v>220000</v>
+        <v>19500</v>
       </c>
       <c r="I35" s="3">
         <v>-8200</v>
@@ -2418,8 +2418,8 @@
       <c r="H41" s="3">
         <v>68600</v>
       </c>
-      <c r="I41" s="3">
-        <v>84600</v>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J41" s="3">
         <v>86800</v>
@@ -2463,25 +2463,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>54600</v>
+        <v>57300</v>
       </c>
       <c r="E42" s="3">
         <v>56500</v>
       </c>
       <c r="F42" s="3">
-        <v>84200</v>
+        <v>87500</v>
       </c>
       <c r="G42" s="3">
-        <v>83900</v>
+        <v>87300</v>
       </c>
       <c r="H42" s="3">
         <v>69300</v>
       </c>
       <c r="I42" s="3">
-        <v>27200</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>50400</v>
+        <v>53400</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -2534,10 +2534,10 @@
         <v>44600</v>
       </c>
       <c r="H43" s="3">
-        <v>39600</v>
-      </c>
-      <c r="I43" s="3">
-        <v>51500</v>
+        <v>41600</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
         <v>42900</v>
@@ -2580,26 +2580,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2640,25 +2640,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5300</v>
+        <v>2400</v>
       </c>
       <c r="E45" s="3">
-        <v>5800</v>
+        <v>2500</v>
       </c>
       <c r="F45" s="3">
-        <v>9000</v>
+        <v>2400</v>
       </c>
       <c r="G45" s="3">
-        <v>9100</v>
+        <v>2400</v>
       </c>
       <c r="H45" s="3">
-        <v>7900</v>
-      </c>
-      <c r="I45" s="3">
         <v>2500</v>
       </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="J45" s="3">
-        <v>8800</v>
+        <v>2500</v>
       </c>
       <c r="K45" s="3">
         <v>22400</v>
@@ -2713,8 +2713,8 @@
       <c r="H46" s="3">
         <v>185300</v>
       </c>
-      <c r="I46" s="3">
-        <v>165900</v>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J46" s="3">
         <v>188900</v>
@@ -2761,7 +2761,7 @@
         <v>34900</v>
       </c>
       <c r="E47" s="3">
-        <v>19400</v>
+        <v>19100</v>
       </c>
       <c r="F47" s="3">
         <v>18100</v>
@@ -2772,11 +2772,11 @@
       <c r="H47" s="3">
         <v>18500</v>
       </c>
-      <c r="I47" s="3">
-        <v>17300</v>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J47" s="3">
-        <v>21200</v>
+        <v>17900</v>
       </c>
       <c r="K47" s="3">
         <v>36500</v>
@@ -2831,8 +2831,8 @@
       <c r="H48" s="3">
         <v>2400</v>
       </c>
-      <c r="I48" s="3">
-        <v>3600</v>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J48" s="3">
         <v>2200</v>
@@ -2891,7 +2891,7 @@
         <v>12600</v>
       </c>
       <c r="I49" s="3">
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>14800</v>
@@ -3053,25 +3053,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>73400</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>87700</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>74200</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>77100</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>83400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>73300</v>
+        <v>100</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
-        <v>94900</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>111600</v>
@@ -3185,8 +3185,8 @@
       <c r="H54" s="3">
         <v>302200</v>
       </c>
-      <c r="I54" s="3">
-        <v>269300</v>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J54" s="3">
         <v>322000</v>
@@ -3288,10 +3288,10 @@
         <v>14000</v>
       </c>
       <c r="H57" s="3">
-        <v>15000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>28500</v>
+        <v>28300</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J57" s="3">
         <v>22300</v>
@@ -3350,7 +3350,7 @@
         <v>800</v>
       </c>
       <c r="I58" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>700</v>
@@ -3394,25 +3394,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>265800</v>
+        <v>255200</v>
       </c>
       <c r="E59" s="3">
         <v>290600</v>
       </c>
       <c r="F59" s="3">
-        <v>279600</v>
+        <v>272200</v>
       </c>
       <c r="G59" s="3">
-        <v>286100</v>
+        <v>275700</v>
       </c>
       <c r="H59" s="3">
-        <v>312300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>252600</v>
+        <v>299100</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3">
-        <v>309400</v>
+        <v>301600</v>
       </c>
       <c r="K59" s="3">
         <v>316300</v>
@@ -3467,8 +3467,8 @@
       <c r="H60" s="3">
         <v>328100</v>
       </c>
-      <c r="I60" s="3">
-        <v>282200</v>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J60" s="3">
         <v>332400</v>
@@ -3527,7 +3527,7 @@
         <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>400</v>
@@ -3571,25 +3571,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>119500</v>
+        <v>1000</v>
       </c>
       <c r="E62" s="3">
-        <v>128200</v>
+        <v>35900</v>
       </c>
       <c r="F62" s="3">
-        <v>116600</v>
+        <v>1300</v>
       </c>
       <c r="G62" s="3">
-        <v>116700</v>
+        <v>3000</v>
       </c>
       <c r="H62" s="3">
-        <v>109700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>120100</v>
+        <v>9200</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
-        <v>138000</v>
+        <v>41100</v>
       </c>
       <c r="K62" s="3">
         <v>151200</v>
@@ -3821,8 +3821,8 @@
       <c r="H66" s="3">
         <v>437900</v>
       </c>
-      <c r="I66" s="3">
-        <v>403200</v>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J66" s="3">
         <v>470800</v>
@@ -4125,25 +4125,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-111300</v>
+        <v>-260800</v>
       </c>
       <c r="E72" s="3">
-        <v>-156800</v>
+        <v>-328400</v>
       </c>
       <c r="F72" s="3">
-        <v>-125300</v>
+        <v>-274100</v>
       </c>
       <c r="G72" s="3">
-        <v>-136200</v>
+        <v>-285200</v>
       </c>
       <c r="H72" s="3">
-        <v>-159800</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-134000</v>
+        <v>-308900</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J72" s="3">
-        <v>-172500</v>
+        <v>-320200</v>
       </c>
       <c r="K72" s="3">
         <v>-104900</v>
@@ -4376,7 +4376,7 @@
         <v>-135800</v>
       </c>
       <c r="I76" s="3">
-        <v>-134000</v>
+        <v>-148800</v>
       </c>
       <c r="J76" s="3">
         <v>-148800</v>
@@ -4555,7 +4555,7 @@
         <v>23700</v>
       </c>
       <c r="H81" s="3">
-        <v>220000</v>
+        <v>19500</v>
       </c>
       <c r="I81" s="3">
         <v>-8200</v>
@@ -4625,25 +4625,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="E83" s="3">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="F83" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="G83" s="3">
         <v>1700</v>
       </c>
       <c r="H83" s="3">
-        <v>2900</v>
+        <v>2200</v>
       </c>
       <c r="I83" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="J83" s="3">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="K83" s="3">
         <v>3600</v>
@@ -4991,7 +4991,7 @@
         <v>8000</v>
       </c>
       <c r="H89" s="3">
-        <v>-100</v>
+        <v>11900</v>
       </c>
       <c r="I89" s="3">
         <v>-12100</v>
@@ -5070,16 +5070,16 @@
         <v>-400</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -5250,7 +5250,7 @@
         <v>-14200</v>
       </c>
       <c r="H94" s="3">
-        <v>-18300</v>
+        <v>-12800</v>
       </c>
       <c r="I94" s="3">
         <v>-5400</v>
@@ -5319,26 +5319,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5568,7 +5568,7 @@
         <v>-1200</v>
       </c>
       <c r="H100" s="3">
-        <v>-800</v>
+        <v>-200</v>
       </c>
       <c r="I100" s="3">
         <v>-600</v>
@@ -5615,25 +5615,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F101" s="3">
-        <v>700</v>
+        <v>1800</v>
       </c>
       <c r="G101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>200</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
-      </c>
-      <c r="H101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J101" s="3">
-        <v>1800</v>
       </c>
       <c r="K101" s="3">
         <v>1400</v>
@@ -5686,7 +5686,7 @@
         <v>-7600</v>
       </c>
       <c r="H102" s="3">
-        <v>-18200</v>
+        <v>300</v>
       </c>
       <c r="I102" s="3">
         <v>-18400</v>

--- a/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>GDEV</t>
   </si>
@@ -656,276 +656,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>110700</v>
+      </c>
+      <c r="E8" s="3">
         <v>105800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>106900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>109100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>121300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>114900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>119300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>103100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>252800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>126100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>122600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>115200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>109600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>86700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>74400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>64500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>63300</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E9" s="3">
         <v>35400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>36200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>37600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>39900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>40700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>43400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>56500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>89400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>38500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>32500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>22600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>22000</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E10" s="3">
         <v>70400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>70700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>71600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>81400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>74200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>75900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>46600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>163400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>89400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>84100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>82700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>78500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>60000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>47500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>41900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>41300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,8 +960,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,47 +1082,50 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>63400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>125400</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,46 +1141,49 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1600</v>
       </c>
       <c r="F15" s="3">
         <v>1600</v>
       </c>
       <c r="G15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H15" s="3">
         <v>1700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>100</v>
@@ -1169,7 +1192,7 @@
         <v>100</v>
       </c>
       <c r="Q15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R15" s="3">
         <v>200</v>
@@ -1177,14 +1200,17 @@
       <c r="S15" s="3">
         <v>200</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>200</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E17" s="3">
         <v>90800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>108800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>101100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>92300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>132700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>137500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>202600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>100200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>99600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>226600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>125200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>93800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>69200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>76200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>53500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E18" s="3">
         <v>15000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>29000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-34500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>50200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-111400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9800</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,161 +1377,168 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E21" s="3">
         <v>15800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>25900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>21600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-34700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>58500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>34500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-97900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-14200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-10800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>10800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>2500</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>100</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
       </c>
       <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1521,99 +1561,105 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E23" s="3">
         <v>15700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>25300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>19800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-100800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>54800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>18300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-98600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10600</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
-      </c>
-      <c r="M24" s="3">
-        <v>300</v>
       </c>
       <c r="N24" s="3">
         <v>300</v>
@@ -1622,25 +1668,28 @@
         <v>300</v>
       </c>
       <c r="P24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
-      </c>
-      <c r="R24" s="3">
-        <v>200</v>
       </c>
       <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>200</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E26" s="3">
         <v>14700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>52700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>32200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-98800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-11200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10400</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E27" s="3">
         <v>14700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-77000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>53100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>32300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>18000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-98800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-11200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10400</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1899,29 +1960,29 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>23400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-11500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-8800</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3">
-        <v>-4900</v>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="3">
         <v>-4900</v>
       </c>
       <c r="P29" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E33" s="3">
         <v>14700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-77000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>41500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>23400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>18000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-103700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10400</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E35" s="3">
         <v>14700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-77000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>41500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>23400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>18000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-103700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10400</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,50 +2484,51 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E41" s="3">
         <v>50800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>71800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>68600</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3">
         <v>86800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>91400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>83700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>142800</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3">
         <v>40900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2457,35 +2544,38 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E42" s="3">
         <v>57300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>56500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>87500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>87300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>69300</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>53400</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2498,8 +2588,8 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2516,50 +2606,53 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>49100</v>
+      </c>
+      <c r="E43" s="3">
         <v>52200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>41800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>48800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>44600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>41600</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3">
         <v>42900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>44700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>46500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>42800</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3">
         <v>63500</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,11 +2665,14 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2601,8 +2697,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2634,50 +2730,53 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E45" s="3">
         <v>2400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2400</v>
       </c>
       <c r="G45" s="3">
         <v>2400</v>
       </c>
       <c r="H45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I45" s="3">
         <v>2500</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>2500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5600</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>4800</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,50 +2792,53 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>168300</v>
+      </c>
+      <c r="E46" s="3">
         <v>162900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>172400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>213900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>198600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>185300</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="3">
         <v>188900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>158500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>139300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>191100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3">
         <v>109100</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2752,41 +2854,44 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E47" s="3">
         <v>34900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>18100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>18500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>17900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>36500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>36800</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2796,8 +2901,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2805,56 +2910,59 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2400</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3">
-        <v>2200</v>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>2200</v>
       </c>
       <c r="L48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M48" s="3">
         <v>4100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3400</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3">
         <v>2900</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2867,53 +2975,56 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E49" s="3">
         <v>8300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12600</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>14800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>64500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>65900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1800</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3">
         <v>1600</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,11 +3037,14 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3164,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3067,30 +3187,30 @@
       <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="I52" s="3">
         <v>100</v>
       </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="K52" s="3">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3">
         <v>111600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>125700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>116700</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
         <v>105200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3103,11 +3223,14 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,50 +3288,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>283400</v>
+      </c>
+      <c r="E54" s="3">
         <v>282800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>295600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>320600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>307500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>302200</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K54" s="3">
         <v>322000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>373300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>371700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>313000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3">
         <v>218900</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,50 +3400,51 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>32700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28300</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>22300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3">
         <v>20900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3329,50 +3460,53 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>800</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
         <v>1300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3385,53 +3519,56 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E59" s="3">
         <v>255200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>290600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>272200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>275700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>299100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>301600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>316300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>319200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>305800</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>275900</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3447,50 +3584,53 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>277200</v>
+      </c>
+      <c r="E60" s="3">
         <v>281100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>324000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>302800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>301300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>328100</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
         <v>332400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>326800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>342900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>322800</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3">
         <v>298100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,50 +3646,53 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>1000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>200</v>
-      </c>
-      <c r="F61" s="3">
-        <v>1000</v>
       </c>
       <c r="G61" s="3">
         <v>1000</v>
       </c>
       <c r="H61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>400</v>
       </c>
       <c r="L61" s="3">
+        <v>400</v>
+      </c>
+      <c r="M61" s="3">
         <v>900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3565,8 +3708,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3574,41 +3720,41 @@
         <v>1000</v>
       </c>
       <c r="E62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F62" s="3">
         <v>35900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9200</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>41100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>151200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>166900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>150100</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>105600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,50 +3956,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>386500</v>
+      </c>
+      <c r="E66" s="3">
         <v>401500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>452400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>420400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>419000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>437900</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K66" s="3">
         <v>470800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>478200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>510700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>474100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3">
         <v>404200</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3860,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,50 +4290,53 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-246200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-260800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-328400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-274100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-285200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-308900</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>-320200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-104900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-139000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-161100</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3">
         <v>-185400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,50 +4538,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-103100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-118700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-156800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-99800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-111500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-135800</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-148800</v>
       </c>
       <c r="J76" s="3">
         <v>-148800</v>
       </c>
       <c r="K76" s="3">
+        <v>-148800</v>
+      </c>
+      <c r="L76" s="3">
         <v>-104900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-139000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-161100</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3">
         <v>-185400</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4414,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E81" s="3">
         <v>14700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-77000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>41500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>23400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>18000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-103700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10400</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,52 +4817,53 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E83" s="3">
         <v>1500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>600</v>
       </c>
       <c r="O83" s="3">
         <v>600</v>
       </c>
       <c r="P83" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q83" s="3">
         <v>500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
@@ -4673,13 +4872,16 @@
         <v>200</v>
       </c>
       <c r="T83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E89" s="3">
         <v>11300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>39600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>43700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>51000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>18500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>41500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>32400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>40000</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,8 +5275,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5067,55 +5288,58 @@
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-400</v>
       </c>
       <c r="O91" s="3">
         <v>-400</v>
       </c>
       <c r="P91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5459,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-45300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>56000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-63100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-83300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-77100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5340,8 +5574,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,181 +5793,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-43600</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>14100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-50700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-34000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-9700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1100</v>
-      </c>
-      <c r="R101" s="3">
-        <v>400</v>
       </c>
       <c r="S101" s="3">
         <v>400</v>
       </c>
       <c r="T101" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-33900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-44800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-43700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-59100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>37300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>64600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-59000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>23400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>35400</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
   <si>
     <t>GDEV</t>
   </si>
@@ -656,289 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>97500</v>
+      </c>
+      <c r="E8" s="3">
         <v>110700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>105800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>106900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>109100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>121300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>114900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>119300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>103100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>252800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>126100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>122600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>115200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>109600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>86700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>74400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>64500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>63300</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E9" s="3">
         <v>36600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>35400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>36200</v>
       </c>
-      <c r="G9" s="3">
-        <v>37600</v>
-      </c>
       <c r="H9" s="3">
+        <v>41500</v>
+      </c>
+      <c r="I9" s="3">
         <v>39900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>40700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>43400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>56500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>89400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>38500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>32500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>22600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>22000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E10" s="3">
         <v>74100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>70400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>70700</v>
       </c>
-      <c r="G10" s="3">
-        <v>71600</v>
-      </c>
       <c r="H10" s="3">
+        <v>67600</v>
+      </c>
+      <c r="I10" s="3">
         <v>81400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>74200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>75900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>46600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>163400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>89400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>84100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>82700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>78500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>60000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>47500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>41900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>41300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1023,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,25 +1101,28 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>100</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1111,24 +1130,24 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>63400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>125400</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1144,49 +1163,52 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>800</v>
+      </c>
+      <c r="E15" s="3">
         <v>1600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1600</v>
       </c>
       <c r="G15" s="3">
         <v>1600</v>
       </c>
       <c r="H15" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I15" s="3">
         <v>1700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>800</v>
-      </c>
-      <c r="O15" s="3">
-        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>100</v>
@@ -1195,7 +1217,7 @@
         <v>100</v>
       </c>
       <c r="R15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S15" s="3">
         <v>200</v>
@@ -1203,14 +1225,17 @@
       <c r="T15" s="3">
         <v>200</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>200</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>84800</v>
+      </c>
+      <c r="E17" s="3">
         <v>96000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>90800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>108800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>101100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>92300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>100100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>132700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>137500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>202600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>100200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>99600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>226600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>125200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>93800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>69200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>76200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>53500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E18" s="3">
         <v>14600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>29000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-34500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>50200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>23000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-111400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9800</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,170 +1410,177 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-4100</v>
-      </c>
       <c r="H20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I20" s="3">
         <v>4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
         <v>17700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3500</v>
       </c>
-      <c r="G21" s="3">
-        <v>13700</v>
-      </c>
       <c r="H21" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I21" s="3">
         <v>25900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>21600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-34700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>58500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>34500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-97900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-10800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>2500</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1564,105 +1603,111 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>16100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>25300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>19800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-100800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>54800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>33000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>18300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-98600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10600</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
-      </c>
-      <c r="N24" s="3">
-        <v>300</v>
       </c>
       <c r="O24" s="3">
         <v>300</v>
@@ -1671,25 +1716,28 @@
         <v>300</v>
       </c>
       <c r="Q24" s="3">
+        <v>300</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
-      </c>
-      <c r="S24" s="3">
-        <v>200</v>
       </c>
       <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>200</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E26" s="3">
         <v>14600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>23700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-100400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>52700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>32200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-98800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E27" s="3">
         <v>14600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>23700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-77000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>53100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>32300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-98800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1963,29 +2023,29 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>23400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-11500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-8800</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O29" s="3">
-        <v>-4900</v>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P29" s="3">
         <v>-4900</v>
       </c>
       <c r="Q29" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="R29" s="3">
         <v>-2600</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3800</v>
       </c>
-      <c r="G32" s="3">
-        <v>4100</v>
-      </c>
       <c r="H32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E33" s="3">
         <v>14600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>14700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>23700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-77000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>41500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>23400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-103700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-11800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E35" s="3">
         <v>14600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>14700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>23700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-77000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>41500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>23400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-103700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-11800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,53 +2570,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E41" s="3">
         <v>86600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>50800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>68300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>71800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>61000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>68600</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3">
         <v>86800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>91400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>83700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>142800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3">
         <v>40900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,38 +2633,41 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E42" s="3">
         <v>30100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>57300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>56500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>87500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>87300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>69300</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>53400</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2591,8 +2680,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2609,53 +2698,56 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E43" s="3">
         <v>49100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>52200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>41800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>44600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>41600</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>42900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>44700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>46500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>42800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
         <v>63500</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2668,11 +2760,14 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2700,8 +2795,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2733,8 +2828,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2742,44 +2840,44 @@
         <v>2200</v>
       </c>
       <c r="E45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F45" s="3">
         <v>2400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2400</v>
       </c>
       <c r="H45" s="3">
         <v>2400</v>
       </c>
       <c r="I45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J45" s="3">
         <v>2500</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>2500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5600</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>4800</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,53 +2893,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>179600</v>
+      </c>
+      <c r="E46" s="3">
         <v>168300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>162900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>172400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>213900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>198600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>185300</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3">
         <v>188900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>158500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>139300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>191100</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3">
         <v>109100</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,44 +2958,47 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E47" s="3">
         <v>36200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>34900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>19100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>18100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>18500</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>17900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>36500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>36800</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,8 +3008,8 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -2913,59 +3017,62 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>0</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E48" s="3">
         <v>3000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3">
-        <v>2200</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L48" s="3">
         <v>2200</v>
       </c>
       <c r="M48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N48" s="3">
         <v>4100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3">
         <v>2900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,56 +3085,59 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E49" s="3">
         <v>7300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12600</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>14800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>64500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>65900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1800</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3">
         <v>1600</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3040,11 +3150,14 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,8 +3283,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3190,30 +3309,30 @@
       <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="J52" s="3">
         <v>100</v>
       </c>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="L52" s="3">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3">
         <v>111600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>125700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>116700</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3">
         <v>105200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3226,11 +3345,14 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,53 +3413,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>272200</v>
+      </c>
+      <c r="E54" s="3">
         <v>283400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>282800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>295600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>320600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>307500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>302200</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3">
         <v>322000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>373300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>371700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>313000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3">
         <v>218900</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,53 +3530,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E57" s="3">
         <v>29000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28300</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>22300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3">
         <v>20900</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,53 +3593,56 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>800</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3522,56 +3655,59 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>242600</v>
+      </c>
+      <c r="E59" s="3">
         <v>247000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>255200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>290600</v>
       </c>
-      <c r="G59" s="3">
-        <v>272200</v>
-      </c>
       <c r="H59" s="3">
+        <v>271900</v>
+      </c>
+      <c r="I59" s="3">
         <v>275700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>299100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>301600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>316300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>319200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>305800</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>275900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,53 +3723,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>263500</v>
+      </c>
+      <c r="E60" s="3">
         <v>277200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>281100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>324000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>302800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>301300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>328100</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3">
         <v>332400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>326800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>342900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>322800</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3">
         <v>298100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3649,8 +3788,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3658,44 +3800,44 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>1000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>200</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1000</v>
       </c>
       <c r="H61" s="3">
         <v>1000</v>
       </c>
       <c r="I61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>400</v>
       </c>
       <c r="M61" s="3">
+        <v>400</v>
+      </c>
+      <c r="N61" s="3">
         <v>900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3711,53 +3853,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
         <v>1000</v>
       </c>
       <c r="F62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G62" s="3">
         <v>35900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9200</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>41100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>151200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>166900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>150100</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>105600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3773,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,53 +4113,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>373700</v>
+      </c>
+      <c r="E66" s="3">
         <v>386500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>401500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>452400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>420400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>419000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>437900</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3">
         <v>470800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>478200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>510700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>474100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3">
         <v>404200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4021,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,53 +4463,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-248500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-246200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-260800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-328400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-274100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-285200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-308900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
         <v>-320200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-104900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-139000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-161100</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-185400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4355,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,53 +4723,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-101500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-103100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-118700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-156800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-99800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-111500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-135800</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-148800</v>
       </c>
       <c r="K76" s="3">
         <v>-148800</v>
       </c>
       <c r="L76" s="3">
+        <v>-148800</v>
+      </c>
+      <c r="M76" s="3">
         <v>-104900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-139000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-161100</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3">
         <v>-185400</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4603,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E81" s="3">
         <v>14600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>14700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>23700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-77000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>41500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>23400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-103700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-11800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,55 +5015,56 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>600</v>
       </c>
       <c r="P83" s="3">
         <v>600</v>
       </c>
       <c r="Q83" s="3">
+        <v>600</v>
+      </c>
+      <c r="R83" s="3">
         <v>500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>200</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
@@ -4875,13 +5073,16 @@
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E89" s="3">
         <v>11900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>39600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>43700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>51000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>18500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>41500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>32400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>40000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5291,55 +5511,58 @@
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-400</v>
       </c>
       <c r="P91" s="3">
         <v>-400</v>
       </c>
       <c r="Q91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E94" s="3">
         <v>24300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-45300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>56000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-63100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-83300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-77100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1400</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5577,8 +5810,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-43600</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>14100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-50700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-34000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-9700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1100</v>
-      </c>
-      <c r="S101" s="3">
-        <v>400</v>
       </c>
       <c r="T101" s="3">
         <v>400</v>
       </c>
       <c r="U101" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E102" s="3">
         <v>35800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-33900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-44800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-43700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-59100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>37300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>64600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>23400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>35400</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="92">
   <si>
     <t>GDEV</t>
   </si>
@@ -762,23 +762,23 @@
       <c r="D8" s="3">
         <v>97500</v>
       </c>
-      <c r="E8" s="3">
-        <v>110700</v>
-      </c>
-      <c r="F8" s="3">
-        <v>105800</v>
-      </c>
-      <c r="G8" s="3">
-        <v>106900</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
         <v>109100</v>
       </c>
-      <c r="I8" s="3">
-        <v>121300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>114900</v>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>119300</v>
@@ -827,23 +827,23 @@
       <c r="D9" s="3">
         <v>33800</v>
       </c>
-      <c r="E9" s="3">
-        <v>36600</v>
-      </c>
-      <c r="F9" s="3">
-        <v>35400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>36200</v>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
         <v>41500</v>
       </c>
-      <c r="I9" s="3">
-        <v>39900</v>
-      </c>
-      <c r="J9" s="3">
-        <v>40700</v>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>43400</v>
@@ -892,23 +892,23 @@
       <c r="D10" s="3">
         <v>63700</v>
       </c>
-      <c r="E10" s="3">
-        <v>74100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>70400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>70700</v>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>67600</v>
       </c>
-      <c r="I10" s="3">
-        <v>81400</v>
-      </c>
-      <c r="J10" s="3">
-        <v>74200</v>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <v>75900</v>
@@ -1115,8 +1115,8 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>400</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -1178,22 +1178,22 @@
         <v>800</v>
       </c>
       <c r="E15" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>-4700</v>
       </c>
       <c r="I15" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>1400</v>
@@ -1264,23 +1264,23 @@
       <c r="D17" s="3">
         <v>84800</v>
       </c>
-      <c r="E17" s="3">
-        <v>96000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>90800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>108800</v>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H17" s="3">
         <v>101100</v>
       </c>
-      <c r="I17" s="3">
-        <v>92300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>100100</v>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3">
         <v>132700</v>
@@ -1329,23 +1329,23 @@
       <c r="D18" s="3">
         <v>12700</v>
       </c>
-      <c r="E18" s="3">
-        <v>14600</v>
-      </c>
-      <c r="F18" s="3">
-        <v>15000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1900</v>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
         <v>8000</v>
       </c>
-      <c r="I18" s="3">
-        <v>29000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>14800</v>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3">
         <v>-13500</v>
@@ -1419,23 +1419,23 @@
       <c r="D20" s="3">
         <v>15200</v>
       </c>
-      <c r="E20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-3800</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>-3000</v>
       </c>
-      <c r="I20" s="3">
-        <v>4800</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-5300</v>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>-4700</v>
@@ -1485,22 +1485,22 @@
         <v>-1600</v>
       </c>
       <c r="E21" s="3">
-        <v>17700</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
-        <v>15800</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>6300</v>
       </c>
       <c r="I21" s="3">
-        <v>25900</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>21600</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>-7300</v>
@@ -1552,20 +1552,20 @@
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2500</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>200</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1614,23 +1614,23 @@
       <c r="D23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
-        <v>16100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>15700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-600</v>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H23" s="3">
         <v>12300</v>
       </c>
-      <c r="I23" s="3">
-        <v>25300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>19800</v>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3">
         <v>-7400</v>
@@ -1679,23 +1679,23 @@
       <c r="D24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>900</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J24" s="3">
-        <v>300</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>700</v>
@@ -1809,23 +1809,23 @@
       <c r="D26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
-        <v>14600</v>
-      </c>
-      <c r="F26" s="3">
-        <v>14700</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-1400</v>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H26" s="3">
         <v>11100</v>
       </c>
-      <c r="I26" s="3">
-        <v>23700</v>
-      </c>
-      <c r="J26" s="3">
-        <v>19500</v>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3">
         <v>-8200</v>
@@ -1874,23 +1874,23 @@
       <c r="D27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
-        <v>14600</v>
-      </c>
-      <c r="F27" s="3">
-        <v>14700</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1400</v>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H27" s="3">
         <v>11100</v>
       </c>
-      <c r="I27" s="3">
-        <v>23700</v>
-      </c>
-      <c r="J27" s="3">
-        <v>19500</v>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3">
         <v>-8200</v>
@@ -2199,23 +2199,23 @@
       <c r="D32" s="3">
         <v>-15200</v>
       </c>
-      <c r="E32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>3800</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>3000</v>
       </c>
-      <c r="I32" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="J32" s="3">
-        <v>5300</v>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>4700</v>
@@ -2264,23 +2264,23 @@
       <c r="D33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
-        <v>14600</v>
-      </c>
-      <c r="F33" s="3">
-        <v>14700</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-1400</v>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H33" s="3">
         <v>11100</v>
       </c>
-      <c r="I33" s="3">
-        <v>23700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>19500</v>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>-8200</v>
@@ -2394,23 +2394,23 @@
       <c r="D35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
-        <v>14600</v>
-      </c>
-      <c r="F35" s="3">
-        <v>14700</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-1400</v>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H35" s="3">
         <v>11100</v>
       </c>
-      <c r="I35" s="3">
-        <v>23700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>19500</v>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3">
         <v>-8200</v>
@@ -2579,23 +2579,23 @@
       <c r="D41" s="3">
         <v>111000</v>
       </c>
-      <c r="E41" s="3">
-        <v>86600</v>
-      </c>
-      <c r="F41" s="3">
-        <v>50800</v>
-      </c>
-      <c r="G41" s="3">
-        <v>68300</v>
+      <c r="E41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3">
         <v>71800</v>
       </c>
-      <c r="I41" s="3">
-        <v>61000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>68600</v>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -2645,22 +2645,22 @@
         <v>28000</v>
       </c>
       <c r="E42" s="3">
-        <v>30100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>57300</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>56500</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>87500</v>
       </c>
       <c r="I42" s="3">
-        <v>87300</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>69300</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2709,23 +2709,23 @@
       <c r="D43" s="3">
         <v>38100</v>
       </c>
-      <c r="E43" s="3">
-        <v>49100</v>
-      </c>
-      <c r="F43" s="3">
-        <v>52200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>41800</v>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>48800</v>
       </c>
-      <c r="I43" s="3">
-        <v>44600</v>
-      </c>
-      <c r="J43" s="3">
-        <v>41600</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2839,23 +2839,23 @@
       <c r="D45" s="3">
         <v>2200</v>
       </c>
-      <c r="E45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2500</v>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
         <v>2400</v>
       </c>
-      <c r="I45" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>2500</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2904,23 +2904,23 @@
       <c r="D46" s="3">
         <v>179600</v>
       </c>
-      <c r="E46" s="3">
-        <v>168300</v>
-      </c>
-      <c r="F46" s="3">
-        <v>162900</v>
-      </c>
-      <c r="G46" s="3">
-        <v>172400</v>
+      <c r="E46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3">
         <v>213900</v>
       </c>
-      <c r="I46" s="3">
-        <v>198600</v>
-      </c>
-      <c r="J46" s="3">
-        <v>185300</v>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2969,23 +2969,23 @@
       <c r="D47" s="3">
         <v>16100</v>
       </c>
-      <c r="E47" s="3">
-        <v>36200</v>
-      </c>
-      <c r="F47" s="3">
-        <v>34900</v>
-      </c>
-      <c r="G47" s="3">
-        <v>19100</v>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3">
         <v>18100</v>
       </c>
-      <c r="I47" s="3">
-        <v>16200</v>
-      </c>
-      <c r="J47" s="3">
-        <v>18500</v>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -3034,23 +3034,23 @@
       <c r="D48" s="3">
         <v>2900</v>
       </c>
-      <c r="E48" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2400</v>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
         <v>4100</v>
       </c>
-      <c r="I48" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>2400</v>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -3099,23 +3099,23 @@
       <c r="D49" s="3">
         <v>6300</v>
       </c>
-      <c r="E49" s="3">
-        <v>7300</v>
-      </c>
-      <c r="F49" s="3">
-        <v>8300</v>
-      </c>
-      <c r="G49" s="3">
-        <v>13700</v>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H49" s="3">
         <v>10300</v>
       </c>
-      <c r="I49" s="3">
-        <v>11400</v>
-      </c>
-      <c r="J49" s="3">
-        <v>12600</v>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -3294,23 +3294,23 @@
       <c r="D52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
-        <v>100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
-        <v>100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -3424,23 +3424,23 @@
       <c r="D54" s="3">
         <v>272200</v>
       </c>
-      <c r="E54" s="3">
-        <v>283400</v>
-      </c>
-      <c r="F54" s="3">
-        <v>282800</v>
-      </c>
-      <c r="G54" s="3">
-        <v>295600</v>
+      <c r="E54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3">
         <v>320600</v>
       </c>
-      <c r="I54" s="3">
-        <v>307500</v>
-      </c>
-      <c r="J54" s="3">
-        <v>302200</v>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -3539,23 +3539,23 @@
       <c r="D57" s="3">
         <v>12900</v>
       </c>
-      <c r="E57" s="3">
-        <v>29000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>14100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>32700</v>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
         <v>21700</v>
       </c>
-      <c r="I57" s="3">
-        <v>14000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>28300</v>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -3604,23 +3604,23 @@
       <c r="D58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>700</v>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="I58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>800</v>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3669,23 +3669,23 @@
       <c r="D59" s="3">
         <v>242600</v>
       </c>
-      <c r="E59" s="3">
-        <v>247000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>255200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>290600</v>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
         <v>271900</v>
       </c>
-      <c r="I59" s="3">
-        <v>275700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>299100</v>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -3734,23 +3734,23 @@
       <c r="D60" s="3">
         <v>263500</v>
       </c>
-      <c r="E60" s="3">
-        <v>277200</v>
-      </c>
-      <c r="F60" s="3">
-        <v>281100</v>
-      </c>
-      <c r="G60" s="3">
-        <v>324000</v>
+      <c r="E60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3">
         <v>302800</v>
       </c>
-      <c r="I60" s="3">
-        <v>301300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>328100</v>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -3803,19 +3803,19 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>1000</v>
       </c>
       <c r="I61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3864,23 +3864,23 @@
       <c r="D62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>35900</v>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
         <v>1300</v>
       </c>
-      <c r="I62" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>9200</v>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -4124,23 +4124,23 @@
       <c r="D66" s="3">
         <v>373700</v>
       </c>
-      <c r="E66" s="3">
-        <v>386500</v>
-      </c>
-      <c r="F66" s="3">
-        <v>401500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>452400</v>
+      <c r="E66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3">
         <v>420400</v>
       </c>
-      <c r="I66" s="3">
-        <v>419000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>437900</v>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -4474,23 +4474,23 @@
       <c r="D72" s="3">
         <v>-248500</v>
       </c>
-      <c r="E72" s="3">
-        <v>-246200</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-260800</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-328400</v>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3">
         <v>-274100</v>
       </c>
-      <c r="I72" s="3">
-        <v>-285200</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-308900</v>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -4734,23 +4734,23 @@
       <c r="D76" s="3">
         <v>-101500</v>
       </c>
-      <c r="E76" s="3">
-        <v>-103100</v>
-      </c>
-      <c r="F76" s="3">
-        <v>-118700</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-156800</v>
+      <c r="E76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3">
         <v>-99800</v>
       </c>
-      <c r="I76" s="3">
-        <v>-111500</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-135800</v>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3">
         <v>-148800</v>
@@ -4934,23 +4934,23 @@
       <c r="D81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
-        <v>14600</v>
-      </c>
-      <c r="F81" s="3">
-        <v>14700</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-1400</v>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H81" s="3">
         <v>11100</v>
       </c>
-      <c r="I81" s="3">
-        <v>23700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>19500</v>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3">
         <v>-8200</v>
@@ -5024,20 +5024,20 @@
       <c r="D83" s="3">
         <v>1600</v>
       </c>
-      <c r="E83" s="3">
-        <v>1700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1400</v>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3">
         <v>1500</v>
       </c>
-      <c r="I83" s="3">
-        <v>1700</v>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3">
         <v>2200</v>
@@ -5414,23 +5414,23 @@
       <c r="D89" s="3">
         <v>4900</v>
       </c>
-      <c r="E89" s="3">
-        <v>11900</v>
-      </c>
-      <c r="F89" s="3">
-        <v>11300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>400</v>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H89" s="3">
         <v>10000</v>
       </c>
-      <c r="I89" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J89" s="3">
-        <v>11900</v>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3">
         <v>-12100</v>
@@ -5504,23 +5504,23 @@
       <c r="D91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -5699,23 +5699,23 @@
       <c r="D94" s="3">
         <v>20900</v>
       </c>
-      <c r="E94" s="3">
-        <v>24300</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-45300</v>
-      </c>
-      <c r="G94" s="3">
-        <v>56000</v>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3">
         <v>100</v>
       </c>
-      <c r="I94" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-12800</v>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>-5400</v>
@@ -6049,23 +6049,23 @@
       <c r="D100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-43600</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
-      <c r="I100" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-200</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>-600</v>
@@ -6114,20 +6114,20 @@
       <c r="D101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F101" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-300</v>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
         <v>1800</v>
       </c>
-      <c r="I101" s="3">
-        <v>-1600</v>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J101" s="3">
         <v>1100</v>
@@ -6180,22 +6180,22 @@
         <v>24500</v>
       </c>
       <c r="E102" s="3">
-        <v>35800</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>-33900</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>10800</v>
       </c>
       <c r="I102" s="3">
-        <v>-7600</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>-18400</v>

--- a/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="92">
   <si>
     <t>GDEV</t>
   </si>
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E8" s="3">
         <v>119900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>108500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>97500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>105800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>106900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>109100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>103100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
         <v>119300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>103100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>252800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>126100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>122600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>115200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>109600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>86700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>74400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>64500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>63300</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E9" s="3">
         <v>39400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>36800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>33800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>35400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>36200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>41500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>56500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3">
         <v>43400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>56500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>89400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>36700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>38500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>32500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>31100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>22600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>22000</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E10" s="3">
         <v>80500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>71700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>63700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>70400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>70700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>67600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>46600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3">
         <v>75900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>46600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>163400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>89400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>84100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>82700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>78500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>60000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>47500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>41900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>41300</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,59 +1161,62 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>63400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>63400</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>125400</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1212,58 +1232,61 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="3">
         <v>1200</v>
       </c>
       <c r="F15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G15" s="3">
         <v>800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-4700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
       <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>1400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>800</v>
-      </c>
-      <c r="R15" s="3">
-        <v>100</v>
       </c>
       <c r="S15" s="3">
         <v>100</v>
@@ -1272,7 +1295,7 @@
         <v>100</v>
       </c>
       <c r="U15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V15" s="3">
         <v>200</v>
@@ -1280,14 +1303,17 @@
       <c r="W15" s="3">
         <v>200</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E17" s="3">
         <v>101300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>92200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>84800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>90600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>107000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>101100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>137500</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3">
         <v>132700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>137500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>202600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>100200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>99600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>226600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>125200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>93800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>69200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>76200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>53500</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E18" s="3">
         <v>18600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15200</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
       <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>8000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-34500</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-13500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-34500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>50200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>25900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>23000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-111400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-11700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9800</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,155 +1512,162 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>15200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3600</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>-4700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>12800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>800</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E21" s="3">
         <v>19300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>15800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-34700</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
       <c r="L21" s="3">
         <v>0</v>
       </c>
       <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-7300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-34700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>58500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>34500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>19200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-97900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-14200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-10800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10800</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1645,31 +1685,31 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>100</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1692,123 +1732,129 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E23" s="3">
         <v>18200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>16900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>15700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-100800</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3">
         <v>-7400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-100800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>54800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>18300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-98600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-14800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10600</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>300</v>
       </c>
       <c r="R24" s="3">
         <v>300</v>
@@ -1817,25 +1863,28 @@
         <v>300</v>
       </c>
       <c r="T24" s="3">
+        <v>300</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
-      </c>
-      <c r="V24" s="3">
-        <v>200</v>
       </c>
       <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E26" s="3">
         <v>16600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100400</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3">
         <v>-8200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-100400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>52700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>32200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-98800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-15100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10400</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E27" s="3">
         <v>16600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-77000</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3">
         <v>-8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-77000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>53100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>32300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-98800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-15100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10400</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2142,11 +2203,11 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>23400</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
@@ -2154,29 +2215,29 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>23400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-11500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R29" s="3">
-        <v>-4900</v>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>-4900</v>
       </c>
       <c r="T29" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="U29" s="3">
         <v>-2600</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-15200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3600</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>4700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-12800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-800</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E33" s="3">
         <v>16600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-77000</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3">
         <v>-8200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-77000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>41500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>23400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-103700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10400</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E35" s="3">
         <v>16600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-77000</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3">
         <v>-8200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-77000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>41500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>23400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-103700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10400</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,62 +2831,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E41" s="3">
         <v>41600</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3">
         <v>111000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>50800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>68300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>71800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>86800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3">
         <v>86800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>91400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>83700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>142800</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3">
         <v>40900</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,35 +2903,38 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E42" s="3">
         <v>38100</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>28000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>57300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>56500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>87500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>53400</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2852,11 +2942,11 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>53400</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2869,8 +2959,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2887,62 +2977,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E43" s="3">
         <v>46800</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3">
         <v>38100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>52200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>41800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>48800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>42900</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3">
         <v>42900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>44700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>42800</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3">
         <v>63500</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2955,11 +3048,14 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2996,8 +3092,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3029,62 +3125,65 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E45" s="3">
         <v>2000</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>2200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2500</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3">
         <v>2500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5600</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3">
         <v>4800</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3100,62 +3199,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>155100</v>
+      </c>
+      <c r="E46" s="3">
         <v>128700</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3">
         <v>179600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>162900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>172400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>213900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>188900</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3">
         <v>188900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>158500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>139300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>191100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3">
         <v>109100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3171,53 +3273,56 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E47" s="3">
         <v>16600</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3">
         <v>16100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>34900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>19100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>18100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>17900</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>17900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>36500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>36800</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,8 +3332,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3236,68 +3341,71 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
+      <c r="X47" s="3">
+        <v>0</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E48" s="3">
         <v>3100</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3">
         <v>2900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3">
-        <v>2200</v>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O48" s="3">
         <v>2200</v>
       </c>
       <c r="P48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q48" s="3">
         <v>4100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3400</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3">
         <v>2900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3310,65 +3418,68 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E49" s="3">
         <v>4100</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>6300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14800</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>14800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>64500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>65900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1800</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S49" s="3">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3">
         <v>1600</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,11 +3492,14 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,19 +3643,22 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3">
-        <v>100</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
@@ -3552,8 +3672,8 @@
       <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>100</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
@@ -3561,27 +3681,27 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>111600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>125700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>116700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3">
         <v>105200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,11 +3714,14 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,62 +3791,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>233100</v>
+      </c>
+      <c r="E54" s="3">
         <v>210200</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3">
         <v>272200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>282800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>295600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>320600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>322000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3">
         <v>322000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>373300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>371700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>313000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3">
         <v>218900</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,62 +3923,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E57" s="3">
         <v>12900</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3">
         <v>12900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22300</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3">
         <v>22300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16200</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3">
         <v>20900</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,62 +3995,65 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1700</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>800</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
         <v>1300</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,65 +4066,68 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E59" s="3">
         <v>226000</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
         <v>242600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>255200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>290600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>271900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>301400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3">
         <v>301600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>316300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>319200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>305800</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3">
         <v>275900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4006,62 +4143,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>231900</v>
+      </c>
+      <c r="E60" s="3">
         <v>250000</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3">
         <v>263500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>281100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>324000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>302800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>332400</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3">
         <v>332400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>326800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>342900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>322800</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3">
         <v>298100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4077,35 +4217,38 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>600</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>1000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4113,26 +4256,26 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>400</v>
       </c>
       <c r="P61" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q61" s="3">
         <v>900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1100</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>600</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4148,62 +4291,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
         <v>300</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>35900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>41100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
         <v>41100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>151200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>166900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>150100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3">
         <v>105600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,62 +4587,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>323700</v>
+      </c>
+      <c r="E66" s="3">
         <v>339600</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3">
         <v>373700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>401500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>452400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>420400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>470800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3">
         <v>470800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>478200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>510700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>474100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3">
         <v>404200</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,62 +4985,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-239200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-277700</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3">
         <v>-248500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-260800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-328400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-274100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-320200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3">
         <v>-320200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-104900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-139000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-161100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3">
         <v>-185400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,62 +5281,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-90600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-129400</v>
-      </c>
-      <c r="E76" s="3">
-        <v>-101500</v>
       </c>
       <c r="F76" s="3">
         <v>-101500</v>
       </c>
       <c r="G76" s="3">
+        <v>-101500</v>
+      </c>
+      <c r="H76" s="3">
         <v>-118700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-156800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-99800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-148800</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3">
-        <v>-148800</v>
+      <c r="M76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N76" s="3">
         <v>-148800</v>
       </c>
       <c r="O76" s="3">
+        <v>-148800</v>
+      </c>
+      <c r="P76" s="3">
         <v>-104900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-139000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-161100</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3">
         <v>-185400</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E81" s="3">
         <v>16600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-77000</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3">
         <v>-8200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-77000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>41500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>23400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-103700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10400</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,64 +5612,65 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="E83" s="3">
         <v>1600</v>
       </c>
       <c r="F83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>600</v>
       </c>
       <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="K83" s="3">
+        <v>600</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>2200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>800</v>
-      </c>
-      <c r="R83" s="3">
-        <v>600</v>
       </c>
       <c r="S83" s="3">
         <v>600</v>
       </c>
       <c r="T83" s="3">
+        <v>600</v>
+      </c>
+      <c r="U83" s="3">
         <v>500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
@@ -5480,13 +5679,16 @@
         <v>200</v>
       </c>
       <c r="X83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1900</v>
+        <v>18400</v>
       </c>
       <c r="E89" s="3">
         <v>-1900</v>
       </c>
       <c r="F89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G89" s="3">
         <v>4900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-12100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>16800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>39600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>18400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>43700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>51000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>18500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>41500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>32400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>40000</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,13 +6158,14 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
@@ -5959,58 +6180,61 @@
         <v>-100</v>
       </c>
       <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-400</v>
       </c>
       <c r="S91" s="3">
         <v>-400</v>
       </c>
       <c r="T91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5700</v>
+        <v>-10200</v>
       </c>
       <c r="E94" s="3">
         <v>-5700</v>
       </c>
       <c r="F94" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="G94" s="3">
         <v>20900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-45300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>56000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-63100</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-5400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-63100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-83300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-77100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1400</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,13 +6482,14 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>3</v>
+      <c r="D96" s="3">
+        <v>0</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>3</v>
@@ -6287,8 +6521,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,217 +6776,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-28200</v>
+        <v>-500</v>
       </c>
       <c r="E100" s="3">
         <v>-28200</v>
       </c>
       <c r="F100" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-43600</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>-600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>14100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-50700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-34000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-9700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5100</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1100</v>
-      </c>
-      <c r="V101" s="3">
-        <v>400</v>
       </c>
       <c r="W101" s="3">
         <v>400</v>
       </c>
       <c r="X101" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-34700</v>
+        <v>7900</v>
       </c>
       <c r="E102" s="3">
         <v>-34700</v>
       </c>
       <c r="F102" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="G102" s="3">
         <v>24500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-44800</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-18400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-44800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-43700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-59100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>37300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>64600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-59000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>23400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>35400</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
